--- a/jira_export_2026-09-18.xlsx
+++ b/jira_export_2026-09-18.xlsx
@@ -818,7 +818,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>280 h</t>
+          <t>284 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -832,7 +832,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -936,7 +936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P163"/>
+  <dimension ref="A1:P164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1392,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>3</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>568.8</v>
       </c>
       <c r="P58" s="15" t="n">
-        <v>0</v>
+        <v>568.8</v>
       </c>
     </row>
     <row r="59">
@@ -11439,22 +11439,22 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C152" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E152" s="14" t="n">
@@ -11477,14 +11477,14 @@
       </c>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J152" s="14" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K152" s="14" t="n">
-        <v>3.58</v>
+        <v>0.75</v>
       </c>
       <c r="L152" s="14" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -11501,22 +11501,22 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
@@ -11529,35 +11529,27 @@
       </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I153" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J153" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K153" s="11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L153" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M153" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>3.58</v>
+      </c>
+      <c r="L153" s="11" t="inlineStr"/>
+      <c r="M153" s="11" t="inlineStr"/>
       <c r="N153" s="12" t="n">
         <v>0</v>
       </c>
@@ -11571,22 +11563,22 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B154" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C154" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D154" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E154" s="14" t="n">
@@ -11599,23 +11591,35 @@
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H154" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H154" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I154" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J154" s="14" t="n">
         <v>36</v>
       </c>
       <c r="K154" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L154" s="14" t="inlineStr"/>
-      <c r="M154" s="14" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L154" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M154" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N154" s="15" t="n">
         <v>0</v>
       </c>
@@ -11629,12 +11633,12 @@
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr">
@@ -11644,7 +11648,7 @@
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E155" s="11" t="n">
@@ -11660,32 +11664,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H155" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H155" s="11" t="inlineStr"/>
       <c r="I155" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J155" s="11" t="n">
         <v>36</v>
       </c>
       <c r="K155" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L155" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M155" s="11" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L155" s="11" t="inlineStr"/>
+      <c r="M155" s="11" t="inlineStr"/>
       <c r="N155" s="12" t="n">
         <v>0</v>
       </c>
@@ -11699,28 +11691,26 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B156" s="14" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C156" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D156" s="14" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E156" s="14" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E156" s="14" t="n">
+        <v/>
       </c>
       <c r="F156" s="14" t="inlineStr">
         <is>
@@ -11734,22 +11724,30 @@
       </c>
       <c r="H156" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I156" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J156" s="14" t="n">
         <v>36</v>
       </c>
       <c r="K156" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L156" s="14" t="inlineStr"/>
-      <c r="M156" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L156" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M156" s="14" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N156" s="15" t="n">
         <v>0</v>
       </c>
@@ -11763,23 +11761,27 @@
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C157" s="11" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C157" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F157" s="11" t="inlineStr">
@@ -11794,19 +11796,19 @@
       </c>
       <c r="H157" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I157" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J157" s="11" t="n">
         <v>36</v>
       </c>
       <c r="K157" s="11" t="n">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="L157" s="11" t="inlineStr"/>
       <c r="M157" s="11" t="inlineStr"/>
@@ -11823,21 +11825,25 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B158" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C158" s="14" t="inlineStr"/>
       <c r="D158" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E158" s="14" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E158" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F158" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11845,26 +11851,26 @@
       </c>
       <c r="G158" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H158" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H158" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I158" s="14" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J158" s="14" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K158" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L158" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="L158" s="14" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
       <c r="N158" s="15" t="n">
         <v>0</v>
@@ -11879,18 +11885,18 @@
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>PSC-1334</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr"/>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr"/>
@@ -11901,7 +11907,7 @@
       </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr"/>
@@ -11914,9 +11920,13 @@
         <v>2</v>
       </c>
       <c r="K159" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L159" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L159" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
       <c r="M159" s="11" t="inlineStr"/>
       <c r="N159" s="12" t="n">
         <v>0</v>
@@ -11931,18 +11941,18 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1334</t>
         </is>
       </c>
       <c r="B160" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="C160" s="14" t="inlineStr"/>
       <c r="D160" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="E160" s="14" t="inlineStr"/>
@@ -11953,31 +11963,23 @@
       </c>
       <c r="G160" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H160" s="14" t="inlineStr"/>
       <c r="I160" s="14" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J160" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K160" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L160" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M160" s="14" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L160" s="14" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
       <c r="N160" s="15" t="n">
         <v>0</v>
       </c>
@@ -11991,18 +11993,18 @@
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr"/>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr"/>
@@ -12019,23 +12021,23 @@
       <c r="H161" s="11" t="inlineStr"/>
       <c r="I161" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J161" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K161" s="11" t="n">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="L161" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-34778</t>
         </is>
       </c>
       <c r="M161" s="11" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00172868</t>
         </is>
       </c>
       <c r="N161" s="12" t="n">
@@ -12051,18 +12053,18 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>PSC-668</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B162" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C162" s="14" t="inlineStr"/>
       <c r="D162" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E162" s="14" t="inlineStr"/>
@@ -12073,59 +12075,119 @@
       </c>
       <c r="G162" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H162" s="14" t="inlineStr"/>
       <c r="I162" s="14" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J162" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K162" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L162" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M162" s="14" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N162" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="10" t="inlineStr">
+        <is>
+          <t>PSC-668</t>
+        </is>
+      </c>
+      <c r="B163" s="11" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="C163" s="11" t="inlineStr"/>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="E163" s="11" t="inlineStr"/>
+      <c r="F163" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G163" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H163" s="11" t="inlineStr"/>
+      <c r="I163" s="11" t="inlineStr">
+        <is>
           <t>04/04/2025</t>
         </is>
       </c>
-      <c r="J162" s="14" t="n">
+      <c r="J163" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="K162" s="14" t="n">
+      <c r="K163" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L162" s="14" t="inlineStr"/>
-      <c r="M162" s="14" t="inlineStr"/>
-      <c r="N162" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O162" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P162" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="17" t="inlineStr">
+      <c r="L163" s="11" t="inlineStr"/>
+      <c r="M163" s="11" t="inlineStr"/>
+      <c r="N163" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B163" s="17" t="inlineStr"/>
-      <c r="C163" s="17" t="inlineStr"/>
-      <c r="D163" s="17" t="inlineStr"/>
-      <c r="E163" s="17" t="inlineStr"/>
-      <c r="F163" s="17" t="inlineStr"/>
-      <c r="G163" s="17" t="inlineStr"/>
-      <c r="H163" s="17" t="inlineStr"/>
-      <c r="I163" s="17" t="inlineStr"/>
-      <c r="J163" s="17" t="inlineStr"/>
-      <c r="K163" s="17" t="inlineStr"/>
-      <c r="L163" s="17" t="inlineStr"/>
-      <c r="M163" s="17" t="inlineStr"/>
-      <c r="N163" s="18" t="n">
+      <c r="B164" s="17" t="inlineStr"/>
+      <c r="C164" s="17" t="inlineStr"/>
+      <c r="D164" s="17" t="inlineStr"/>
+      <c r="E164" s="17" t="inlineStr"/>
+      <c r="F164" s="17" t="inlineStr"/>
+      <c r="G164" s="17" t="inlineStr"/>
+      <c r="H164" s="17" t="inlineStr"/>
+      <c r="I164" s="17" t="inlineStr"/>
+      <c r="J164" s="17" t="inlineStr"/>
+      <c r="K164" s="17" t="inlineStr"/>
+      <c r="L164" s="17" t="inlineStr"/>
+      <c r="M164" s="17" t="inlineStr"/>
+      <c r="N164" s="18" t="n">
         <v>48290.375</v>
       </c>
-      <c r="O163" s="18" t="n">
+      <c r="O164" s="18" t="n">
         <v>25776.268</v>
       </c>
-      <c r="P163" s="18" t="n">
-        <v>144.36</v>
+      <c r="P164" s="18" t="n">
+        <v>142.17</v>
       </c>
     </row>
   </sheetData>
@@ -12289,6 +12351,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId159"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13373,13 +13436,13 @@
         <v>93.67</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>29.92</v>
+        <v>30.67</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>12</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>135.58</v>
+        <v>136.33</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>20.42</v>
@@ -13389,7 +13452,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>20.9%</t>
         </is>
       </c>
     </row>
@@ -13400,7 +13463,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>38.75</v>
+        <v>40.75</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -13409,7 +13472,7 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>41.25</v>
+        <v>43.25</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>5.5</v>
@@ -13419,7 +13482,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.7%</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13494,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>74</v>
+        <v>75.5</v>
       </c>
     </row>
   </sheetData>
@@ -13519,16 +13582,16 @@
         <v>396392</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>173628</v>
+        <v>171123</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>222763</v>
+        <v>225268</v>
       </c>
       <c r="E5" s="24" t="n">
         <v>137774</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>18223</v>
+        <v>20728</v>
       </c>
       <c r="G5" s="24" t="n">
         <v>21338</v>
@@ -13569,16 +13632,16 @@
         <v>224850</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>103312</v>
+        <v>100807</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>121537</v>
+        <v>124042</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>51433</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>9048</v>
+        <v>11553</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>18153</v>

--- a/jira_export_2026-09-18.xlsx
+++ b/jira_export_2026-09-18.xlsx
@@ -723,7 +723,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>25,776 €</t>
+          <t>26,408 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -737,7 +737,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -770,7 +770,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>17,406 €</t>
+          <t>18,038 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -818,7 +818,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>284 h</t>
+          <t>302 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -832,7 +832,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -889,7 +889,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -936,7 +936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P164"/>
+  <dimension ref="A1:P165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -2172,7 +2172,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="L20" s="14" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -2236,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>8</v>
+        <v>8.75</v>
       </c>
       <c r="L21" s="11" t="inlineStr"/>
       <c r="M21" s="11" t="inlineStr"/>
@@ -3020,7 +3020,7 @@
         <v>2</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>5.75</v>
+        <v>8.25</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>215</v>
       </c>
       <c r="P32" s="15" t="n">
-        <v>37.39</v>
+        <v>26.06</v>
       </c>
     </row>
     <row r="33">
@@ -4308,7 +4308,7 @@
         <v>3</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>418</v>
       </c>
       <c r="P50" s="15" t="n">
-        <v>278.67</v>
+        <v>92.89</v>
       </c>
     </row>
     <row r="51">
@@ -4452,7 +4452,7 @@
         <v>3</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>65.73</v>
       </c>
       <c r="P52" s="15" t="n">
-        <v>23.9</v>
+        <v>21.91</v>
       </c>
     </row>
     <row r="53">
@@ -4596,7 +4596,7 @@
         <v>3</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>465.85</v>
       </c>
       <c r="P54" s="15" t="n">
-        <v>66.55</v>
+        <v>58.23</v>
       </c>
     </row>
     <row r="55">
@@ -4900,10 +4900,10 @@
         <v>0</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>568.8</v>
+        <v>1200.8</v>
       </c>
       <c r="P58" s="15" t="n">
-        <v>568.8</v>
+        <v>1200.8</v>
       </c>
     </row>
     <row r="59">
@@ -10424,7 +10424,7 @@
         <v>18</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="L136" s="14" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>21</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>13.08</v>
+        <v>15.08</v>
       </c>
       <c r="L142" s="14" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -12053,18 +12053,18 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B162" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C162" s="14" t="inlineStr"/>
       <c r="D162" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E162" s="14" t="inlineStr"/>
@@ -12075,31 +12075,23 @@
       </c>
       <c r="G162" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H162" s="14" t="inlineStr"/>
       <c r="I162" s="14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J162" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K162" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L162" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M162" s="14" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L162" s="14" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
       <c r="N162" s="15" t="n">
         <v>0</v>
       </c>
@@ -12113,18 +12105,18 @@
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
         <is>
-          <t>PSC-668</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr"/>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr"/>
@@ -12135,59 +12127,119 @@
       </c>
       <c r="G163" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr"/>
       <c r="I163" s="11" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J163" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K163" s="11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L163" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M163" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N163" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="13" t="inlineStr">
+        <is>
+          <t>PSC-668</t>
+        </is>
+      </c>
+      <c r="B164" s="14" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="C164" s="14" t="inlineStr"/>
+      <c r="D164" s="14" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="E164" s="14" t="inlineStr"/>
+      <c r="F164" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G164" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H164" s="14" t="inlineStr"/>
+      <c r="I164" s="14" t="inlineStr">
+        <is>
           <t>04/04/2025</t>
         </is>
       </c>
-      <c r="J163" s="11" t="n">
+      <c r="J164" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="K163" s="11" t="n">
+      <c r="K164" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L163" s="11" t="inlineStr"/>
-      <c r="M163" s="11" t="inlineStr"/>
-      <c r="N163" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O163" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P163" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="17" t="inlineStr">
+      <c r="L164" s="14" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+      <c r="N164" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B164" s="17" t="inlineStr"/>
-      <c r="C164" s="17" t="inlineStr"/>
-      <c r="D164" s="17" t="inlineStr"/>
-      <c r="E164" s="17" t="inlineStr"/>
-      <c r="F164" s="17" t="inlineStr"/>
-      <c r="G164" s="17" t="inlineStr"/>
-      <c r="H164" s="17" t="inlineStr"/>
-      <c r="I164" s="17" t="inlineStr"/>
-      <c r="J164" s="17" t="inlineStr"/>
-      <c r="K164" s="17" t="inlineStr"/>
-      <c r="L164" s="17" t="inlineStr"/>
-      <c r="M164" s="17" t="inlineStr"/>
-      <c r="N164" s="18" t="n">
+      <c r="B165" s="17" t="inlineStr"/>
+      <c r="C165" s="17" t="inlineStr"/>
+      <c r="D165" s="17" t="inlineStr"/>
+      <c r="E165" s="17" t="inlineStr"/>
+      <c r="F165" s="17" t="inlineStr"/>
+      <c r="G165" s="17" t="inlineStr"/>
+      <c r="H165" s="17" t="inlineStr"/>
+      <c r="I165" s="17" t="inlineStr"/>
+      <c r="J165" s="17" t="inlineStr"/>
+      <c r="K165" s="17" t="inlineStr"/>
+      <c r="L165" s="17" t="inlineStr"/>
+      <c r="M165" s="17" t="inlineStr"/>
+      <c r="N165" s="18" t="n">
         <v>48290.375</v>
       </c>
-      <c r="O164" s="18" t="n">
-        <v>25776.268</v>
-      </c>
-      <c r="P164" s="18" t="n">
-        <v>142.17</v>
+      <c r="O165" s="18" t="n">
+        <v>26408.268</v>
+      </c>
+      <c r="P165" s="18" t="n">
+        <v>136.97</v>
       </c>
     </row>
   </sheetData>
@@ -12352,6 +12404,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId160"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13433,26 +13486,26 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>93.67</v>
+        <v>101.92</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>30.67</v>
+        <v>32.67</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>12</v>
+        <v>13.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>136.33</v>
+        <v>147.83</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>20.42</v>
+        <v>22.92</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>652.05</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>22.7%</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13547,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>75.5</v>
+        <v>79.25</v>
       </c>
     </row>
   </sheetData>
@@ -13579,16 +13632,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>396392</v>
+        <v>395760</v>
       </c>
       <c r="C5" s="24" t="n">
         <v>171123</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>225268</v>
+        <v>224636</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>137774</v>
+        <v>137142</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>20728</v>
@@ -13629,16 +13682,16 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>224850</v>
+        <v>224218</v>
       </c>
       <c r="C7" s="26" t="n">
         <v>100807</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>124042</v>
+        <v>123410</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>51433</v>
+        <v>50801</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>11553</v>
@@ -13658,7 +13711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13682,7 +13735,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 22 commande(s)</t>
+          <t>Épics créées ce mois — 23 commande(s)</t>
         </is>
       </c>
     </row>
@@ -13962,22 +14015,22 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35672</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35666</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRISSAC LOIRE AUBANCE</t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -13997,32 +14050,32 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00181382</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>0</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35478</t>
+          <t>PDMDEP-35672</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35666</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>COMMUNE DE BRISSAC LOIRE AUBANCE</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -14042,11 +14095,11 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00180643</t>
+          <t>00181382</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>6285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -14404,22 +14457,22 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35771</t>
+          <t>PDMDEP-35788</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35767</t>
+          <t>PDMDEP-35782</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA HAUTE SAVOIE (CD 74)</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -14439,7 +14492,7 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>00181751</t>
+          <t>00181845</t>
         </is>
       </c>
       <c r="I20" s="26" t="n">
@@ -14629,22 +14682,22 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35771</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35767</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>DEPARTEMENT DE LA HAUTE SAVOIE (CD 74)</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
@@ -14664,83 +14717,107 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00181751</t>
         </is>
       </c>
       <c r="I25" s="25" t="n">
-        <v>895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-35567</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35561</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>00180878</t>
+        </is>
+      </c>
+      <c r="I26" s="26" t="n">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-35622</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-35618</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Commune de la Roche-sur-Yon</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>00181123</t>
         </is>
       </c>
-      <c r="I26" s="26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="17" t="n"/>
-      <c r="G27" s="17" t="n"/>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>22 commande(s)</t>
-        </is>
-      </c>
-      <c r="I27" s="24" t="n">
-        <v>52730</v>
+      <c r="I27" s="25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B28" s="17" t="n"/>
@@ -14751,17 +14828,17 @@
       <c r="G28" s="17" t="n"/>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>10 commande(s)</t>
+          <t>23 commande(s)</t>
         </is>
       </c>
       <c r="I28" s="24" t="n">
-        <v>14880</v>
+        <v>52730</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B29" s="17" t="n"/>
@@ -14772,10 +14849,31 @@
       <c r="G29" s="17" t="n"/>
       <c r="H29" s="17" t="inlineStr">
         <is>
+          <t>11 commande(s)</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="n">
+        <v>14880</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
+      <c r="G30" s="17" t="n"/>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
           <t>12 commande(s)</t>
         </is>
       </c>
-      <c r="I29" s="24" t="n">
+      <c r="I30" s="24" t="n">
         <v>37850</v>
       </c>
     </row>
@@ -14790,7 +14888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -14811,7 +14909,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>8 clôture(s) : 7 projet(s), 1 rework</t>
+          <t>9 clôture(s) : 8 projet(s), 1 rework</t>
         </is>
       </c>
     </row>
@@ -14911,17 +15009,17 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35148</t>
+          <t>PDMDEP-33638</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DES PORTES EN RE] - UPSELL PAX</t>
+          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Les Portes En Ré</t>
+          <t>COMMUNE DE MOULINS</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
@@ -14935,23 +15033,23 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35165</t>
+          <t>PDMDEP-35148</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LORGUES] - Ajout d'une nouvelle régie (Caisse / c</t>
+          <t>[MAIRIE DES PORTES EN RE] - UPSELL PAX</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LORGUES</t>
+          <t>Mairie de Les Portes En Ré</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -14971,17 +15069,17 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35583</t>
+          <t>PDMDEP-35165</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - GeODP - Export CSV spécifique</t>
+          <t>[MAIRIE DE LORGUES] - Ajout d'une nouvelle régie (Caisse / c</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>MAIRIE DE LORGUES</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -14995,18 +15093,18 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-35583</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+          <t>[COMMUNE DE CHAMBERY] - GeODP - Export CSV spécifique</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -15016,7 +15114,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -15025,95 +15123,125 @@
         </is>
       </c>
       <c r="F10" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-32442</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-33699</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assist</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="n">
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>PDMDEP-18196</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>Gentilly</t>
         </is>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E12" s="27" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="F12" s="27" t="n">
+      <c r="F13" s="27" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="17" t="n"/>
-      <c r="F14" s="17" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="28" t="inlineStr">
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B15" s="28" t="n"/>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="28" t="n">
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="28" t="n">
         <v>1</v>
       </c>
     </row>
